--- a/templates/欧代标签-海杰威-129.xlsx
+++ b/templates/欧代标签-海杰威-129.xlsx
@@ -1581,8 +1581,10 @@
       <c r="B1" s="7"/>
     </row>
     <row r="2" s="2" customFormat="1" ht="15.75" spans="1:8">
-      <c r="A2" s="8" t="s">
-        <v>1</v>
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>ItemNo：</t>
+        </is>
       </c>
       <c r="B2" s="9"/>
     </row>
